--- a/9.DCF_Calculation_TESLA-04_Final_project_Excel.xlsx
+++ b/9.DCF_Calculation_TESLA-04_Final_project_Excel.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\Cook N Klean_45-Day's_internship_projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7690A13-2A2A-4719-AD0C-E4A72B6F6B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387D53B5-B1DE-45D9-B9BC-84B37EC6BFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FCF" sheetId="2" r:id="rId1"/>
@@ -356,7 +356,7 @@
     <numFmt numFmtId="173" formatCode="#,##0.00;\(#,##0.00\)"/>
     <numFmt numFmtId="174" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -369,17 +369,20 @@
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -881,6 +884,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -894,12 +903,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1318,7 +1321,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="31.85546875" bestFit="1" customWidth="1"/>
@@ -1330,8 +1333,8 @@
     <col min="12" max="12" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="33.75" customHeight="1" thickBot="1"/>
-    <row r="2" spans="2:8" ht="36.75" customHeight="1" thickTop="1" thickBot="1">
+    <row r="1" spans="2:8" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:8" ht="36.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C2" s="97" t="s">
         <v>102</v>
       </c>
@@ -1340,21 +1343,21 @@
       <c r="F2" s="96"/>
       <c r="G2" s="96"/>
     </row>
-    <row r="3" spans="2:8" ht="15.75" thickTop="1"/>
-    <row r="4" spans="2:8" ht="21" customHeight="1"/>
-    <row r="5" spans="2:8" ht="21" customHeight="1">
-      <c r="B5" s="99" t="s">
+    <row r="3" spans="2:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="101" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="99"/>
-      <c r="D5" s="99"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="99"/>
-      <c r="G5" s="99"/>
-      <c r="H5" s="104"/>
-    </row>
-    <row r="6" spans="2:8" ht="21" customHeight="1">
-      <c r="B6" s="105" t="s">
+      <c r="C5" s="101"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="101"/>
+      <c r="G5" s="101"/>
+      <c r="H5" s="99"/>
+    </row>
+    <row r="6" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="100" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="52">
@@ -1381,7 +1384,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="21" customHeight="1">
+    <row r="7" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>11</v>
       </c>
@@ -1410,7 +1413,7 @@
         <v>147785982.96000004</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="21" customHeight="1">
+    <row r="8" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>12</v>
       </c>
@@ -1439,7 +1442,7 @@
         <v>8.8623538387838478E-3</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="21" customHeight="1">
+    <row r="9" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>13</v>
       </c>
@@ -1468,7 +1471,7 @@
         <v>1309731.6734040007</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="21" customHeight="1">
+    <row r="10" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>66</v>
       </c>
@@ -1497,7 +1500,7 @@
         <v>327432.91835100017</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="21" customHeight="1">
+    <row r="11" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>16</v>
       </c>
@@ -1526,7 +1529,7 @@
         <v>8881937.5758960024</v>
       </c>
     </row>
-    <row r="12" spans="2:8" ht="21" customHeight="1">
+    <row r="12" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>17</v>
       </c>
@@ -1552,7 +1555,7 @@
         <v>-14968091.25</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="21" customHeight="1">
+    <row r="13" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>49</v>
       </c>
@@ -1581,7 +1584,7 @@
         <v>3892051.0125000002</v>
       </c>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="17" t="s">
         <v>67</v>
       </c>
@@ -1610,12 +1613,12 @@
         <v>3176401.416656998</v>
       </c>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B17" s="51"/>
       <c r="C17" s="51"/>
       <c r="D17" s="52">
@@ -1643,10 +1646,10 @@
       </c>
       <c r="L17" s="22"/>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L18" s="22"/>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -1663,7 +1666,7 @@
       <c r="I19" s="20"/>
       <c r="L19" s="22"/>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B20" s="11" t="s">
         <v>11</v>
       </c>
@@ -1692,7 +1695,7 @@
       </c>
       <c r="L20" s="22"/>
     </row>
-    <row r="21" spans="1:12" ht="15.75" thickBot="1">
+    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>51</v>
       </c>
@@ -1720,7 +1723,7 @@
       </c>
       <c r="L21" s="22"/>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B22" s="23" t="s">
         <v>52</v>
       </c>
@@ -1750,7 +1753,7 @@
         <v>29557196.592000008</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15.75" thickBot="1">
+    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>53</v>
       </c>
@@ -1778,7 +1781,7 @@
       </c>
       <c r="L23" s="33"/>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B24" s="23" t="s">
         <v>54</v>
       </c>
@@ -1812,7 +1815,7 @@
         <v>1.1009023789991796</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>55</v>
       </c>
@@ -1839,7 +1842,7 @@
         <v>8881937.5758960024</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="15.75" thickBot="1">
+    <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>56</v>
       </c>
@@ -1866,7 +1869,7 @@
         <v>1631209.3875</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B27" s="23" t="s">
         <v>57</v>
       </c>
@@ -1896,7 +1899,7 @@
         <v>1309731.6734040007</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="15.75" thickBot="1">
+    <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>58</v>
       </c>
@@ -1926,7 +1929,7 @@
       </c>
       <c r="J28" s="22"/>
     </row>
-    <row r="29" spans="1:12" ht="15.75" thickBot="1">
+    <row r="29" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="26" t="s">
         <v>59</v>
       </c>
@@ -1957,7 +1960,7 @@
       </c>
       <c r="J29" s="28"/>
     </row>
-    <row r="30" spans="1:12" ht="15.75" thickTop="1">
+    <row r="30" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
       <c r="D30" s="28"/>
@@ -1967,7 +1970,7 @@
       <c r="H30" s="28"/>
       <c r="I30" s="28"/>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>50</v>
       </c>
@@ -1983,7 +1986,7 @@
       <c r="H31" s="20"/>
       <c r="I31" s="20"/>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>60</v>
       </c>
@@ -2008,7 +2011,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="33" spans="2:12">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>62</v>
       </c>
@@ -2035,7 +2038,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="34" spans="2:12">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>53</v>
       </c>
@@ -2058,7 +2061,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="35" spans="2:12">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>63</v>
       </c>
@@ -2083,7 +2086,7 @@
         <v>6.0100000000000001E-2</v>
       </c>
     </row>
-    <row r="36" spans="2:12">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>64</v>
       </c>
@@ -2106,7 +2109,7 @@
       <c r="J36" s="35"/>
       <c r="K36" s="35"/>
     </row>
-    <row r="37" spans="2:12">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>58</v>
       </c>
@@ -2129,24 +2132,24 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="40" spans="2:12" ht="15.75" customHeight="1">
+    <row r="40" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="11"/>
-      <c r="C40" s="100"/>
-      <c r="D40" s="100"/>
-      <c r="E40" s="100"/>
-      <c r="F40" s="100"/>
-      <c r="G40" s="100"/>
-      <c r="H40" s="100"/>
-      <c r="I40" s="100"/>
-      <c r="J40" s="100"/>
-      <c r="K40" s="100"/>
-      <c r="L40" s="100"/>
-    </row>
-    <row r="41" spans="2:12">
+      <c r="C40" s="102"/>
+      <c r="D40" s="102"/>
+      <c r="E40" s="102"/>
+      <c r="F40" s="102"/>
+      <c r="G40" s="102"/>
+      <c r="H40" s="102"/>
+      <c r="I40" s="102"/>
+      <c r="J40" s="102"/>
+      <c r="K40" s="102"/>
+      <c r="L40" s="102"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C41" s="43"/>
       <c r="D41" s="43"/>
     </row>
-    <row r="47" spans="2:12">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C47" s="33">
         <f>48390000-17626000</f>
         <v>30764000</v>
@@ -2156,7 +2159,7 @@
         <v>3171000</v>
       </c>
     </row>
-    <row r="48" spans="2:12">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E48">
         <f>4576000+12392000+7615000-19449000-1932000</f>
         <v>3202000</v>
@@ -2178,29 +2181,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:D22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
     <col min="2" max="2" width="41.140625" customWidth="1"/>
     <col min="3" max="3" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="21" customHeight="1"/>
-    <row r="2" spans="2:4" ht="21" customHeight="1">
-      <c r="B2" s="101" t="s">
+    <row r="1" spans="2:4" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="103" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102"/>
-    </row>
-    <row r="3" spans="2:4" ht="21" customHeight="1">
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+    </row>
+    <row r="3" spans="2:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="2:4" ht="21" customHeight="1">
+    <row r="4" spans="2:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
         <v>20</v>
       </c>
@@ -2209,7 +2212,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="2:4" ht="21" customHeight="1">
+    <row r="5" spans="2:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="10" t="s">
         <v>21</v>
       </c>
@@ -2218,7 +2221,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="2:4" ht="21" customHeight="1">
+    <row r="6" spans="2:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="10" t="s">
         <v>22</v>
       </c>
@@ -2227,7 +2230,7 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="2:4" ht="21" customHeight="1">
+    <row r="7" spans="2:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="10" t="s">
         <v>23</v>
       </c>
@@ -2237,19 +2240,19 @@
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="2:4" ht="21" customHeight="1">
+    <row r="8" spans="2:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="2:4" ht="21" customHeight="1">
+    <row r="9" spans="2:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="2:4" ht="21" customHeight="1">
+    <row r="10" spans="2:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
         <v>25</v>
       </c>
@@ -2258,7 +2261,7 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="2:4" ht="21" customHeight="1">
+    <row r="11" spans="2:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
         <v>14</v>
       </c>
@@ -2267,7 +2270,7 @@
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="2:4" ht="21" customHeight="1">
+    <row r="12" spans="2:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
         <v>26</v>
       </c>
@@ -2276,26 +2279,26 @@
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="2:4" ht="21" customHeight="1">
+    <row r="13" spans="2:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="10"/>
       <c r="C13" s="5"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="2:4" ht="21" customHeight="1">
+    <row r="14" spans="2:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
         <v>27</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="2:4" ht="21" customHeight="1">
+    <row r="15" spans="2:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="2:4" ht="21" customHeight="1">
+    <row r="16" spans="2:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
         <v>29</v>
       </c>
@@ -2304,7 +2307,7 @@
       </c>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="2:4" ht="21" customHeight="1">
+    <row r="17" spans="2:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
         <v>46</v>
       </c>
@@ -2313,7 +2316,7 @@
       </c>
       <c r="D17" s="1"/>
     </row>
-    <row r="18" spans="2:4" ht="21" customHeight="1">
+    <row r="18" spans="2:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
         <v>30</v>
       </c>
@@ -2322,7 +2325,7 @@
       </c>
       <c r="D18" s="1"/>
     </row>
-    <row r="19" spans="2:4" ht="21" customHeight="1">
+    <row r="19" spans="2:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
         <v>31</v>
       </c>
@@ -2332,7 +2335,7 @@
       </c>
       <c r="D19" s="1"/>
     </row>
-    <row r="20" spans="2:4" ht="21" customHeight="1" thickBot="1">
+    <row r="20" spans="2:4" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="10" t="s">
         <v>32</v>
       </c>
@@ -2342,7 +2345,7 @@
       </c>
       <c r="D20" s="1"/>
     </row>
-    <row r="21" spans="2:4" ht="21" customHeight="1">
+    <row r="21" spans="2:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="16" t="s">
         <v>33</v>
       </c>
@@ -2352,7 +2355,7 @@
       </c>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="2:4">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="3"/>
       <c r="D22" s="1"/>
     </row>
@@ -2367,7 +2370,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:H17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
     <col min="2" max="2" width="27.42578125" customWidth="1"/>
@@ -2379,15 +2382,15 @@
     <col min="8" max="8" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="21" customHeight="1"/>
-    <row r="2" spans="2:8" ht="21" customHeight="1">
-      <c r="B2" s="101" t="s">
+    <row r="1" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="103" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102"/>
-    </row>
-    <row r="3" spans="2:8" ht="21" customHeight="1">
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+    </row>
+    <row r="3" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="10" t="s">
         <v>68</v>
       </c>
@@ -2397,7 +2400,7 @@
       <c r="D3" s="1"/>
       <c r="E3" s="32"/>
     </row>
-    <row r="4" spans="2:8" ht="21" customHeight="1">
+    <row r="4" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
         <v>35</v>
       </c>
@@ -2406,7 +2409,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="2:8" ht="21" customHeight="1">
+    <row r="5" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="10" t="s">
         <v>33</v>
       </c>
@@ -2416,12 +2419,12 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="2:8">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="45" t="s">
         <v>69</v>
       </c>
@@ -2446,7 +2449,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
         <v>54</v>
       </c>
@@ -2475,7 +2478,7 @@
         <v>11822878.636800002</v>
       </c>
     </row>
-    <row r="10" spans="2:8">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
         <v>48</v>
       </c>
@@ -2504,21 +2507,21 @@
         <v>3176401.416656998</v>
       </c>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="F14" s="11" t="s">
         <v>74</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14">
-        <f>H10*(1+C4)/(C3-C4)</f>
-        <v>327169345.91567069</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8">
+        <f>H10*(1+C4)/(C5-C4)</f>
+        <v>44446997.086446442</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="F15" s="11" t="s">
         <v>75</v>
       </c>
@@ -2528,17 +2531,17 @@
         <v>472915.14547200012</v>
       </c>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="F16" s="48" t="s">
         <v>76</v>
       </c>
       <c r="G16" s="48"/>
       <c r="H16" s="49">
         <f>AVERAGE(H14:H15)</f>
-        <v>163821130.53057134</v>
-      </c>
-    </row>
-    <row r="17" spans="6:7">
+        <v>22459956.11595922</v>
+      </c>
+    </row>
+    <row r="17" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
     </row>
@@ -2553,7 +2556,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:I12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.28515625" customWidth="1"/>
@@ -2563,19 +2566,19 @@
     <col min="9" max="9" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="21" customHeight="1"/>
-    <row r="2" spans="2:9" ht="21" customHeight="1">
-      <c r="B2" s="101" t="s">
+    <row r="1" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="103" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102"/>
-      <c r="E2" s="102"/>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
-    </row>
-    <row r="3" spans="2:9" ht="21" customHeight="1">
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="104"/>
+      <c r="H2" s="104"/>
+    </row>
+    <row r="3" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="54"/>
       <c r="C3" s="54"/>
       <c r="D3" s="54"/>
@@ -2584,7 +2587,7 @@
       <c r="G3" s="54"/>
       <c r="H3" s="54"/>
     </row>
-    <row r="4" spans="2:9" ht="21" customHeight="1">
+    <row r="4" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="55" t="s">
         <v>33</v>
       </c>
@@ -2598,7 +2601,7 @@
       <c r="G4" s="54"/>
       <c r="H4" s="54"/>
     </row>
-    <row r="5" spans="2:9" ht="21" customHeight="1">
+    <row r="5" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="54"/>
       <c r="C5" s="54"/>
       <c r="D5" s="54"/>
@@ -2607,7 +2610,7 @@
       <c r="G5" s="54"/>
       <c r="H5" s="54"/>
     </row>
-    <row r="6" spans="2:9" ht="21" customHeight="1">
+    <row r="6" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>5</v>
       </c>
@@ -2633,7 +2636,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="21" customHeight="1">
+    <row r="7" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>48</v>
       </c>
@@ -2663,10 +2666,10 @@
       </c>
       <c r="I7" s="57">
         <f>'Terminal Value'!H14</f>
-        <v>327169345.91567069</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" ht="21" customHeight="1">
+        <v>44446997.086446442</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>37</v>
       </c>
@@ -2692,7 +2695,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="21" customHeight="1">
+    <row r="9" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>38</v>
       </c>
@@ -2725,7 +2728,7 @@
         <v>0.55348887193295937</v>
       </c>
     </row>
-    <row r="10" spans="2:9">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>39</v>
       </c>
@@ -2755,16 +2758,16 @@
       </c>
       <c r="I10" s="58">
         <f>I7*I9</f>
-        <v>181084592.20190874</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9">
+        <v>24600918.278184772</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" s="59" t="s">
         <v>78</v>
       </c>
       <c r="C12" s="95">
         <f>SUM(C10:I10)</f>
-        <v>196151882.24026066</v>
+        <v>39668208.316536702</v>
       </c>
     </row>
   </sheetData>
@@ -2778,7 +2781,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" customWidth="1"/>
     <col min="2" max="2" width="27.7109375" customWidth="1"/>
@@ -2786,25 +2789,25 @@
     <col min="4" max="4" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21" customHeight="1"/>
-    <row r="2" spans="1:4" ht="21" customHeight="1">
-      <c r="B2" s="103" t="s">
+    <row r="1" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="105" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102"/>
-    </row>
-    <row r="3" spans="1:4" ht="21" customHeight="1">
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+    </row>
+    <row r="3" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="60">
         <f>SUM(Discounting!C10:I10)</f>
-        <v>196151882.24026066</v>
+        <v>39668208.316536702</v>
       </c>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="21" customHeight="1">
+    <row r="4" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
         <v>41</v>
       </c>
@@ -2813,7 +2816,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="21" customHeight="1">
+    <row r="5" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="10" t="s">
         <v>42</v>
       </c>
@@ -2822,36 +2825,36 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="21" customHeight="1">
+    <row r="6" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="16" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="93">
         <f>SUM(C3:C5)</f>
-        <v>225491882.24026066</v>
+        <v>69008208.316536695</v>
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="21" customHeight="1">
+    <row r="7" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="10" t="s">
         <v>43</v>
       </c>
       <c r="C7" s="60">
-        <v>3751000</v>
+        <v>375100</v>
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" ht="21" customHeight="1">
+    <row r="8" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="10" t="s">
         <v>44</v>
       </c>
       <c r="C8" s="61">
         <f>C6/C7</f>
-        <v>60.115137893964452</v>
+        <v>183.97282942291841</v>
       </c>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" ht="21" customHeight="1">
+    <row r="9" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
         <v>3</v>
       </c>
@@ -2860,21 +2863,21 @@
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="11"/>
       <c r="B10" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="5">
         <f>C8/C9-1</f>
-        <v>-0.81893030754829987</v>
+        <v>-0.44586497161771566</v>
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="11"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="11"/>
     </row>
   </sheetData>
@@ -2888,7 +2891,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AF7B5DE-D46D-45B3-A323-CCCA549EFA06}">
   <dimension ref="A3:K47"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="33.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.42578125" customWidth="1"/>
@@ -2898,18 +2901,18 @@
     <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:10" ht="21">
-      <c r="B3" s="99" t="s">
+    <row r="3" spans="1:10" ht="21" x14ac:dyDescent="0.25">
+      <c r="B3" s="101" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="99"/>
-    </row>
-    <row r="4" spans="1:10" ht="15.75">
+      <c r="C3" s="101"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="101"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="62"/>
       <c r="B4" s="63"/>
       <c r="C4" s="63"/>
@@ -2920,7 +2923,7 @@
       <c r="H4" s="63"/>
       <c r="I4" s="62"/>
     </row>
-    <row r="5" spans="1:10" ht="15.75">
+    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="64" t="s">
         <v>80</v>
       </c>
@@ -2930,7 +2933,7 @@
       </c>
       <c r="F5" s="64"/>
     </row>
-    <row r="6" spans="1:10" ht="15.75">
+    <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="65" t="s">
         <v>82</v>
       </c>
@@ -2946,7 +2949,7 @@
         <v>1.83</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15.75">
+    <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="65" t="s">
         <v>83</v>
       </c>
@@ -2960,7 +2963,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15.75">
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="65" t="s">
         <v>24</v>
       </c>
@@ -2975,7 +2978,7 @@
         <v>32155000</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.75">
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="65" t="s">
         <v>14</v>
       </c>
@@ -2990,7 +2993,7 @@
         <v>14719000</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.75">
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B10" s="65" t="s">
         <v>87</v>
       </c>
@@ -3000,10 +3003,10 @@
       <c r="E10" s="65"/>
       <c r="F10" s="65"/>
     </row>
-    <row r="11" spans="1:10" ht="15.75">
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C11" s="66"/>
     </row>
-    <row r="13" spans="1:10" ht="15.75">
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="71"/>
       <c r="B13" s="51" t="s">
         <v>69</v>
@@ -3035,7 +3038,7 @@
       </c>
       <c r="J13" s="87"/>
     </row>
-    <row r="14" spans="1:10" ht="15.75">
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="71"/>
       <c r="B14" s="72"/>
       <c r="C14" s="73"/>
@@ -3046,12 +3049,12 @@
       <c r="H14" s="73"/>
       <c r="I14" s="65"/>
     </row>
-    <row r="15" spans="1:10" ht="15.75">
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B15" s="74" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15.75">
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B16" s="71" t="s">
         <v>13</v>
       </c>
@@ -3081,7 +3084,7 @@
         <v>1309731.6734040007</v>
       </c>
     </row>
-    <row r="17" spans="2:11" ht="15.75">
+    <row r="17" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B17" s="71" t="s">
         <v>15</v>
       </c>
@@ -3111,7 +3114,7 @@
         <v>327432.91835100017</v>
       </c>
     </row>
-    <row r="18" spans="2:11" ht="15.75">
+    <row r="18" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B18" s="71" t="s">
         <v>16</v>
       </c>
@@ -3141,7 +3144,7 @@
         <v>8881937.5758960024</v>
       </c>
     </row>
-    <row r="19" spans="2:11" ht="15.75">
+    <row r="19" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B19" s="71" t="s">
         <v>17</v>
       </c>
@@ -3171,7 +3174,7 @@
         <v>-14968091.25</v>
       </c>
     </row>
-    <row r="20" spans="2:11" ht="15.75">
+    <row r="20" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B20" s="71" t="s">
         <v>89</v>
       </c>
@@ -3201,7 +3204,7 @@
         <v>3892051.0125000002</v>
       </c>
     </row>
-    <row r="21" spans="2:11" ht="15.75">
+    <row r="21" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B21" s="77" t="s">
         <v>99</v>
       </c>
@@ -3231,7 +3234,7 @@
         <v>3176401.416656998</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="15.75">
+    <row r="22" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C22" s="75"/>
       <c r="D22" s="75"/>
       <c r="E22" s="75"/>
@@ -3239,7 +3242,7 @@
       <c r="G22" s="75"/>
       <c r="H22" s="75"/>
     </row>
-    <row r="23" spans="2:11" ht="15.75">
+    <row r="23" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B23" s="74" t="s">
         <v>33</v>
       </c>
@@ -3250,7 +3253,7 @@
       <c r="G23" s="75"/>
       <c r="H23" s="75"/>
     </row>
-    <row r="24" spans="2:11" ht="15.75">
+    <row r="24" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B24" s="71" t="s">
         <v>19</v>
       </c>
@@ -3264,7 +3267,7 @@
       <c r="G24" s="75"/>
       <c r="H24" s="75"/>
     </row>
-    <row r="25" spans="2:11" ht="15.75">
+    <row r="25" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B25" s="71" t="s">
         <v>90</v>
       </c>
@@ -3278,7 +3281,7 @@
       <c r="G25" s="75"/>
       <c r="H25" s="75"/>
     </row>
-    <row r="26" spans="2:11" ht="15.75">
+    <row r="26" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B26" s="71" t="s">
         <v>91</v>
       </c>
@@ -3292,7 +3295,7 @@
       <c r="G26" s="75"/>
       <c r="H26" s="75"/>
     </row>
-    <row r="27" spans="2:11" ht="15.75">
+    <row r="27" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B27" s="77" t="s">
         <v>33</v>
       </c>
@@ -3306,7 +3309,7 @@
       <c r="G27" s="75"/>
       <c r="H27" s="75"/>
     </row>
-    <row r="28" spans="2:11" ht="15.75">
+    <row r="28" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C28" s="75"/>
       <c r="D28" s="75"/>
       <c r="E28" s="75"/>
@@ -3314,7 +3317,7 @@
       <c r="G28" s="75"/>
       <c r="H28" s="75"/>
     </row>
-    <row r="29" spans="2:11" ht="15.75">
+    <row r="29" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B29" s="74" t="s">
         <v>77</v>
       </c>
@@ -3326,7 +3329,7 @@
       <c r="H29" s="80"/>
       <c r="I29" s="80"/>
     </row>
-    <row r="30" spans="2:11" ht="15.75">
+    <row r="30" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B30" s="71" t="s">
         <v>54</v>
       </c>
@@ -3340,7 +3343,7 @@
         <v>11822878.636800002</v>
       </c>
     </row>
-    <row r="31" spans="2:11" ht="15.75">
+    <row r="31" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B31" s="71" t="s">
         <v>100</v>
       </c>
@@ -3357,7 +3360,7 @@
       <c r="J31" s="75"/>
       <c r="K31" s="75"/>
     </row>
-    <row r="32" spans="2:11" ht="15.75">
+    <row r="32" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B32" s="71" t="s">
         <v>92</v>
       </c>
@@ -3372,7 +3375,7 @@
         <v>327169345.91567069</v>
       </c>
     </row>
-    <row r="33" spans="2:9" ht="15.75">
+    <row r="33" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B33" s="77" t="s">
         <v>93</v>
       </c>
@@ -3384,10 +3387,10 @@
       <c r="H33" s="78"/>
       <c r="I33" s="78">
         <f>'Terminal Value'!H16</f>
-        <v>163821130.53057134</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9" ht="15.75">
+        <v>22459956.11595922</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C34" s="75"/>
       <c r="D34" s="75"/>
       <c r="E34" s="75"/>
@@ -3395,7 +3398,7 @@
       <c r="G34" s="75"/>
       <c r="H34" s="75"/>
     </row>
-    <row r="35" spans="2:9" ht="15.75">
+    <row r="35" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B35" s="83" t="s">
         <v>94</v>
       </c>
@@ -3407,7 +3410,7 @@
       <c r="H35" s="80"/>
       <c r="I35" s="80"/>
     </row>
-    <row r="36" spans="2:9" ht="15.75">
+    <row r="36" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B36" s="71" t="s">
         <v>38</v>
       </c>
@@ -3437,7 +3440,7 @@
         <v>0.55348887193295937</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="15.75">
+    <row r="37" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B37" s="71" t="s">
         <v>95</v>
       </c>
@@ -3463,7 +3466,7 @@
         <v>2185593.6536470535</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="15.75">
+    <row r="38" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B38" s="98" t="s">
         <v>96</v>
       </c>
@@ -3477,7 +3480,7 @@
         <v>1758102.8369117358</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="15.75">
+    <row r="39" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B39" s="77" t="s">
         <v>0</v>
       </c>
@@ -3489,17 +3492,17 @@
       <c r="H39" s="90"/>
       <c r="I39" s="92">
         <f>Discounting!C12</f>
-        <v>196151882.24026066</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9" ht="15.75">
+        <v>39668208.316536702</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D40" s="75"/>
       <c r="E40" s="75"/>
       <c r="F40" s="75"/>
       <c r="G40" s="75"/>
       <c r="H40" s="75"/>
     </row>
-    <row r="41" spans="2:9" ht="15.75">
+    <row r="41" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B41" s="74" t="s">
         <v>40</v>
       </c>
@@ -3510,7 +3513,7 @@
       <c r="G41" s="75"/>
       <c r="H41" s="75"/>
     </row>
-    <row r="42" spans="2:9" ht="15.75">
+    <row r="42" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B42" s="71" t="s">
         <v>97</v>
       </c>
@@ -3524,7 +3527,7 @@
       <c r="G42" s="75"/>
       <c r="H42" s="75"/>
     </row>
-    <row r="43" spans="2:9" ht="15.75">
+    <row r="43" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B43" s="71" t="s">
         <v>101</v>
       </c>
@@ -3538,13 +3541,13 @@
       <c r="G43" s="75"/>
       <c r="H43" s="75"/>
     </row>
-    <row r="44" spans="2:9" ht="15.75">
+    <row r="44" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B44" s="77" t="s">
         <v>1</v>
       </c>
       <c r="C44" s="79">
         <f>I39+C42+C43</f>
-        <v>225491882.24026066</v>
+        <v>69008208.316536695</v>
       </c>
       <c r="D44" s="75"/>
       <c r="E44" s="75"/>
@@ -3552,7 +3555,7 @@
       <c r="G44" s="75"/>
       <c r="H44" s="75"/>
     </row>
-    <row r="45" spans="2:9" ht="15.75">
+    <row r="45" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C45" s="75"/>
       <c r="D45" s="75"/>
       <c r="E45" s="75"/>
@@ -3560,13 +3563,13 @@
       <c r="G45" s="75"/>
       <c r="H45" s="75"/>
     </row>
-    <row r="46" spans="2:9" ht="15.75">
+    <row r="46" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B46" s="71" t="s">
         <v>2</v>
       </c>
       <c r="C46" s="70">
         <f>'EV to Equity Value'!C7</f>
-        <v>3751000</v>
+        <v>375100</v>
       </c>
       <c r="D46" s="75"/>
       <c r="E46" s="75"/>
@@ -3574,13 +3577,13 @@
       <c r="G46" s="75"/>
       <c r="H46" s="75"/>
     </row>
-    <row r="47" spans="2:9" ht="15.75">
+    <row r="47" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B47" s="77" t="s">
         <v>98</v>
       </c>
       <c r="C47" s="85">
         <f>C44/C46</f>
-        <v>60.115137893964452</v>
+        <v>183.97282942291841</v>
       </c>
       <c r="D47" s="75"/>
       <c r="E47" s="75"/>

--- a/9.DCF_Calculation_TESLA-04_Final_project_Excel.xlsx
+++ b/9.DCF_Calculation_TESLA-04_Final_project_Excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\Cook N Klean_45-Day's_internship_projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387D53B5-B1DE-45D9-B9BC-84B37EC6BFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B4CC1C7-AB9F-43A9-B2D6-4F0090C52B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FCF" sheetId="2" r:id="rId1"/>
@@ -3371,8 +3371,8 @@
       <c r="G32" s="75"/>
       <c r="H32" s="75"/>
       <c r="I32" s="75">
-        <f>'Terminal Value'!H10*(1+'Terminal Value'!$C$4)/('Terminal Value'!$C$3-'Terminal Value'!$C$4)</f>
-        <v>327169345.91567069</v>
+        <f>'Terminal Value'!H10*(1+'Terminal Value'!$C$4)/('Terminal Value'!$C$5-'Terminal Value'!$C$4)</f>
+        <v>44446997.086446442</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">

--- a/9.DCF_Calculation_TESLA-04_Final_project_Excel.xlsx
+++ b/9.DCF_Calculation_TESLA-04_Final_project_Excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\Cook N Klean_45-Day's_internship_projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B4CC1C7-AB9F-43A9-B2D6-4F0090C52B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B39416A-3FC1-4F65-BF5F-C87EAF11FE27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FCF" sheetId="2" r:id="rId1"/>
